--- a/results/0916-all/秦岭大巴山林农区/tech_selected_summary.xlsx
+++ b/results/0916-all/秦岭大巴山林农区/tech_selected_summary.xlsx
@@ -295,208 +295,208 @@
     <t>紫阳县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -595,13 +595,13 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 129022351.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 22788631.63</t>
+    <t>129022351.51</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>22788631.63</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -610,7 +610,7 @@
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 75806191.70</t>
+    <t>75806191.70</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -712,7 +712,7 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 281266637.52</t>
+    <t>281266637.52</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -742,7 +742,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 194887592.77</t>
+    <t>194887592.77</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -751,10 +751,10 @@
     <t>chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 252863719.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 346919743.61</t>
+    <t>252863719.26</t>
+  </si>
+  <si>
+    <t>346919743.61</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
@@ -769,7 +769,7 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 362014788.84</t>
+    <t>362014788.84</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
@@ -778,7 +778,7 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 175265042.96</t>
+    <t>175265042.96</t>
   </si>
   <si>
     <t>Mixture additives _pig</t>
@@ -790,7 +790,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 173737878.25</t>
+    <t>173737878.25</t>
   </si>
   <si>
     <t>Increasing concentrate level (grain)_beef cattle</t>
@@ -823,16 +823,16 @@
     <t>biochar_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 240387919.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 253014792.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 400618383.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 7648260.96</t>
+    <t>240387919.37</t>
+  </si>
+  <si>
+    <t>253014792.88</t>
+  </si>
+  <si>
+    <t>400618383.61</t>
+  </si>
+  <si>
+    <t>7648260.96</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
@@ -841,40 +841,40 @@
     <t>EEF(CRF)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 509169154.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 487847.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 2686595.76</t>
+    <t>509169154.58</t>
+  </si>
+  <si>
+    <t>487847.08</t>
+  </si>
+  <si>
+    <t>2686595.76</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 119608150.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 291961244.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 16981803.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 97064925.84</t>
+    <t>119608150.54</t>
+  </si>
+  <si>
+    <t>291961244.71</t>
+  </si>
+  <si>
+    <t>16981803.49</t>
+  </si>
+  <si>
+    <t>97064925.84</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 351048454.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 54281971.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 162632238.75</t>
+    <t>351048454.01</t>
+  </si>
+  <si>
+    <t>54281971.41</t>
+  </si>
+  <si>
+    <t>162632238.75</t>
   </si>
   <si>
     <t>Mixture additives _dairy</t>
@@ -886,22 +886,22 @@
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 208174882.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 1130922.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 272562427.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 166977468.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 224692393.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 4726186.27</t>
+    <t>208174882.63</t>
+  </si>
+  <si>
+    <t>1130922.48</t>
+  </si>
+  <si>
+    <t>272562427.56</t>
+  </si>
+  <si>
+    <t>166977468.48</t>
+  </si>
+  <si>
+    <t>224692393.63</t>
+  </si>
+  <si>
+    <t>4726186.27</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -910,43 +910,43 @@
     <t>surface crust cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 74057591.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 53496047.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 289125827.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 276554989.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 1982540.67</t>
+    <t>74057591.19</t>
+  </si>
+  <si>
+    <t>53496047.51</t>
+  </si>
+  <si>
+    <t>289125827.85</t>
+  </si>
+  <si>
+    <t>276554989.99</t>
+  </si>
+  <si>
+    <t>1982540.67</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 379209326.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 851526.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 3966.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 21212005.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 7351283.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 177066806.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 23683804.49</t>
+    <t>379209326.76</t>
+  </si>
+  <si>
+    <t>851526.33</t>
+  </si>
+  <si>
+    <t>3966.40</t>
+  </si>
+  <si>
+    <t>21212005.51</t>
+  </si>
+  <si>
+    <t>7351283.99</t>
+  </si>
+  <si>
+    <t>177066806.47</t>
+  </si>
+  <si>
+    <t>23683804.49</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_rice</t>
@@ -955,25 +955,25 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 209619289.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 72349516.13</t>
+    <t>209619289.84</t>
+  </si>
+  <si>
+    <t>72349516.13</t>
   </si>
   <si>
     <t>Chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 553151294.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 53805969.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 447323347.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 224609851.38</t>
+    <t>553151294.12</t>
+  </si>
+  <si>
+    <t>53805969.32</t>
+  </si>
+  <si>
+    <t>447323347.92</t>
+  </si>
+  <si>
+    <t>224609851.38</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
@@ -982,13 +982,13 @@
     <t>manure（high）≥70%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 161104497.42</t>
-  </si>
-  <si>
-    <t>总经济成本: 664443.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 21289345.22</t>
+    <t>161104497.42</t>
+  </si>
+  <si>
+    <t>664443.60</t>
+  </si>
+  <si>
+    <t>21289345.22</t>
   </si>
 </sst>
 </file>
